--- a/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
@@ -3004,7 +3004,7 @@
         <is>
           <t xml:space="preserve">淋·
 △
-湳ㄴ</t>
+湳</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3026,7 +3026,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅋ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3050,19 +3050,19 @@
         <is>
           <t xml:space="preserve">淋·
 △
-湳ㄴ</t>
+湳</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -3110,29 +3110,13 @@
     </row>
     <row r="5" ht="151.44" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="23"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="23"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -3150,11 +3134,7 @@
         </is>
       </c>
       <c r="M5" s="23"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="23"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -3171,52 +3151,31 @@
     </row>
     <row r="6" ht="151.44" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
       <c r="F6" s="21"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
+          <t xml:space="preserve">汰
 南
-ﾉ
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
+          <t xml:space="preserve">汰
 南
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
@@ -3235,9 +3194,9 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ
+          <t xml:space="preserve">湳
 △
-湳ㄴ</t>
+湳</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -3259,7 +3218,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄴ
+          <t xml:space="preserve">南
 汰
 –</t>
         </is>
@@ -3277,7 +3236,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南ㄴ</t>
+南</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -3299,7 +3258,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南ㄴ</t>
+南</t>
         </is>
       </c>
       <c r="S7" s="22"/>
@@ -3309,7 +3268,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-湳ㄴ
+湳
 △</t>
         </is>
       </c>
@@ -3324,18 +3283,15 @@
       <c r="E8" s="23"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-Z
-–</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
+          <t xml:space="preserve">汰
 南∼
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="23"/>
@@ -3343,17 +3299,15 @@
         <is>
           <t xml:space="preserve">林·
 南
-–∼
-‹</t>
+–∼</t>
         </is>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
+          <t xml:space="preserve">汰
 南∼
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M8" s="23"/>
@@ -3369,17 +3323,15 @@
         <is>
           <t xml:space="preserve">林·
 南
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰c
+          <t xml:space="preserve">汰
 南
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="S8" s="23"/>
@@ -3398,12 +3350,7 @@
         </is>
       </c>
       <c r="E9" s="23"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
@@ -3444,17 +3391,9 @@
     </row>
     <row r="10" ht="151.44" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -3462,41 +3401,17 @@
         </is>
       </c>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
@@ -3004,7 +3004,7 @@
         <is>
           <t xml:space="preserve">淋·
 △
-湳</t>
+湳ㄴ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3026,7 +3026,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅋ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3050,19 +3050,19 @@
         <is>
           <t xml:space="preserve">淋·
 △
-湳</t>
+湳ㄴ</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -3110,13 +3110,29 @@
     </row>
     <row r="5" ht="151.44" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C5" s="23"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G5" s="23"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -3134,7 +3150,11 @@
         </is>
       </c>
       <c r="M5" s="23"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O5" s="23"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -3151,7 +3171,11 @@
     </row>
     <row r="6" ht="151.44" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C6" s="24"/>
       <c r="D6" s="21"/>
       <c r="E6" s="24"/>
@@ -3161,21 +3185,26 @@
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰c
 南
+ﾉ
 –</t>
         </is>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰c
 南
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
@@ -3194,9 +3223,9 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳ㄴ
 △
-湳</t>
+湳ㄴ</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -3218,7 +3247,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南ㄴ
 汰
 –</t>
         </is>
@@ -3236,7 +3265,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南</t>
+南ㄴ</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -3258,7 +3287,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南</t>
+南ㄴ</t>
         </is>
       </c>
       <c r="S7" s="22"/>
@@ -3268,7 +3297,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-湳
+湳ㄴ
 △</t>
         </is>
       </c>
@@ -3283,13 +3312,15 @@
       <c r="E8" s="23"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">Z
+Z
+–</t>
         </is>
       </c>
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰c
 南∼
 –</t>
         </is>
@@ -3305,7 +3336,7 @@
       <c r="K8" s="23"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰c
 南∼
 –</t>
         </is>
@@ -3323,15 +3354,15 @@
         <is>
           <t xml:space="preserve">林·
 南
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰c
 南
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="S8" s="23"/>
@@ -3350,7 +3381,12 @@
         </is>
       </c>
       <c r="E9" s="23"/>
-      <c r="F9" s="21"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (자진모리).xlsx
@@ -2950,30 +2950,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="151.44" customHeight="true">
+    <row r="3" ht="159.59" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="151.44" customHeight="true">
+    <row r="4" ht="159.59" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="151.44" customHeight="true">
+    <row r="5" ht="159.59" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="151.44" customHeight="true">
+    <row r="6" ht="159.59" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="151.44" customHeight="true">
+    <row r="7" ht="159.59" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="151.44" customHeight="true">
+    <row r="8" ht="159.59" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="151.44" customHeight="true">
+    <row r="9" ht="159.59" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="151.44" customHeight="true">
+    <row r="10" ht="159.59" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -3456,6 +3456,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>